--- a/data/GreatLink/US Income and Growth Fund (Dis)_Dividends.xlsx
+++ b/data/GreatLink/US Income and Growth Fund (Dis)_Dividends.xlsx
@@ -7,7 +7,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="DividendHistory" sheetId="1" r:id="GemRid744707"/>
+    <sheet name="DividendHistory" sheetId="1" r:id="GemRid685880"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519"/>

--- a/data/GreatLink/US Income and Growth Fund (Dis)_Dividends.xlsx
+++ b/data/GreatLink/US Income and Growth Fund (Dis)_Dividends.xlsx
@@ -7,7 +7,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="DividendHistory" sheetId="1" r:id="GemRid685880"/>
+    <sheet name="DividendHistory" sheetId="1" r:id="GemRid422871"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>XD Date</t>
   </si>
@@ -26,10 +26,13 @@
     <t>Gross Dividend</t>
   </si>
   <si>
+    <t>20/02/2026</t>
+  </si>
+  <si>
+    <t>0.007</t>
+  </si>
+  <si>
     <t>19/01/2026</t>
-  </si>
-  <si>
-    <t>0.007</t>
   </si>
   <si>
     <t>17/12/2025</t>
@@ -520,18 +523,18 @@
         <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -542,7 +545,7 @@
         <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
@@ -553,7 +556,7 @@
         <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
@@ -564,7 +567,7 @@
         <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
@@ -575,7 +578,7 @@
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
@@ -586,7 +589,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
@@ -597,7 +600,7 @@
         <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
@@ -608,7 +611,7 @@
         <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -619,7 +622,7 @@
         <v>18</v>
       </c>
       <c r="C15" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
@@ -630,7 +633,7 @@
         <v>19</v>
       </c>
       <c r="C16" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
@@ -641,7 +644,7 @@
         <v>20</v>
       </c>
       <c r="C17" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -652,18 +655,18 @@
         <v>21</v>
       </c>
       <c r="C18" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C19" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20">
@@ -674,7 +677,7 @@
         <v>24</v>
       </c>
       <c r="C20" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -685,7 +688,7 @@
         <v>25</v>
       </c>
       <c r="C21" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22">
@@ -696,7 +699,7 @@
         <v>26</v>
       </c>
       <c r="C22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23">
@@ -707,7 +710,7 @@
         <v>27</v>
       </c>
       <c r="C23" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24">
@@ -718,7 +721,7 @@
         <v>28</v>
       </c>
       <c r="C24" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25">
@@ -729,7 +732,7 @@
         <v>29</v>
       </c>
       <c r="C25" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26">
@@ -740,7 +743,7 @@
         <v>30</v>
       </c>
       <c r="C26" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27">
@@ -751,7 +754,7 @@
         <v>31</v>
       </c>
       <c r="C27" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28">
@@ -762,7 +765,7 @@
         <v>32</v>
       </c>
       <c r="C28" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29">
@@ -773,7 +776,7 @@
         <v>33</v>
       </c>
       <c r="C29" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="30">
@@ -784,7 +787,7 @@
         <v>34</v>
       </c>
       <c r="C30" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="31">
@@ -795,7 +798,7 @@
         <v>35</v>
       </c>
       <c r="C31" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="32">
@@ -806,7 +809,7 @@
         <v>36</v>
       </c>
       <c r="C32" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
     </row>
     <row r="33">
@@ -828,6 +831,17 @@
         <v>38</v>
       </c>
       <c r="C34" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>39</v>
+      </c>
+      <c r="B35" t="s">
+        <v>39</v>
+      </c>
+      <c r="C35" t="s">
         <v>4</v>
       </c>
     </row>
